--- a/corporate_models/Erdemir_Credit_Model.xlsx
+++ b/corporate_models/Erdemir_Credit_Model.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Credit &amp; Recovery Model" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Credit Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historical Financials &amp; Ratios" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,8 +17,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="5">
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="$#,##0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="0.00&quot;x&quot;"/>
+  </numFmts>
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,8 +33,14 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="14"/>
+      <color rgb="001B365D"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00555555"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -40,14 +51,20 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <sz val="11"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -56,26 +73,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F497D"/>
-        <bgColor rgb="001F497D"/>
+        <fgColor rgb="001B365D"/>
+        <bgColor rgb="001B365D"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00244062"/>
-        <bgColor rgb="00244062"/>
+        <fgColor rgb="00F2F4F8"/>
+        <bgColor rgb="00F2F4F8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DCE6F1"/>
-        <bgColor rgb="00DCE6F1"/>
+        <fgColor rgb="002C3E50"/>
+        <bgColor rgb="002C3E50"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EBF1DE"/>
-        <bgColor rgb="00EBF1DE"/>
+        <fgColor rgb="00E8F8F5"/>
+        <bgColor rgb="00E8F8F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDEDEC"/>
+        <bgColor rgb="00FDEDEC"/>
       </patternFill>
     </fill>
   </fills>
@@ -89,32 +112,54 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="00E0E0E0"/>
       </left>
       <right style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="00E0E0E0"/>
       </right>
       <top style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="00E0E0E0"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="00E0E0E0"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,319 +525,1079 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="B2:E13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="4" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Ereğli Demir Çelik / Erdemir (Turkey) — Institutional Credit &amp; Recovery Model</t>
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Erdemir</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Company &amp; Credit Profile</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Capital Structure ($M)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Sector</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Flat Steel Manufacturing</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Cash &amp; Equivalents</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>650</v>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>CEMBI CEEMEA Assessment | Country: Turkey | Sector: Materials | Benchmark: EREGL 7.95% 2029</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Credit Rating</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>BB- / B1</t>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>TRADING BENCHMARK</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>PRICE / YTM</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Senior Secured Debt</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>350</v>
+          <t>RATINGS &amp; SPREAD</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>STRATEGY STANCE</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Trade Recommendation</t>
-        </is>
-      </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>OVERWEIGHT</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Senior Unsecured Bonds</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>1250</v>
+          <t>Benchmark Bond</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>$98.50 (7.95% YTM)</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>BB- / B1 (+355 bp)</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Overweight / Conviction</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Benchmark Bond Price</t>
-        </is>
-      </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>$97.50</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Bank Syndicated Facilities</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="n">
+          <t>Sector &amp; Product Mix</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Hot Rolled Coil (HRC: 54%), Cold Rolled &amp; Galvanized (32%), Plate &amp; Tinplate (14%)</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Recovery Floor</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>$75.00 (Base $101.00)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>RECOVERY SCENARIO</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>ENTERPRISE VAL</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>BOND RECOVERY</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>IMPLIED PRICE</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Bull Case (Cycle Expansion)</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>115% of Base</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>100% Par</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>$102.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Base Case (Steady Operation)</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>100% Baseline</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>100% Par</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>$101.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Stress Case (Severe Macro Shock)</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>75% Distressed</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>Haircut</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>$88.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Liquidation Floor (Hard Assets/Collateral)</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>45% Fire Sale</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>Collateral Moat</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>$75.00</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:I32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Erdemir — 7-Year Historical &amp; Forecast Financials</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Audited Reported Figures (2021A - 2024A) and Institutional Baseline Projections (2025E - 2027E) | USD Millions</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>FINANCIAL STATEMENT LINE ITEM</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>2021A</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>2022A</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>2023A</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>2024A</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>2025E</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>2027E</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>I. CONSOLIDATED INCOME STATEMENT (USD M)</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="n"/>
+      <c r="D6" s="13" t="n"/>
+      <c r="E6" s="13" t="n"/>
+      <c r="F6" s="13" t="n"/>
+      <c r="G6" s="13" t="n"/>
+      <c r="H6" s="13" t="n"/>
+      <c r="I6" s="13" t="n"/>
+    </row>
+    <row r="7">
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>Revenue / Gross Turnover</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="n">
+        <v>4624</v>
+      </c>
+      <c r="D7" s="15" t="n">
+        <v>5576</v>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>6256</v>
+      </c>
+      <c r="F7" s="15" t="n">
+        <v>6800</v>
+      </c>
+      <c r="G7" s="16" t="n">
+        <v>7344</v>
+      </c>
+      <c r="H7" s="16" t="n">
+        <v>7820</v>
+      </c>
+      <c r="I7" s="16" t="n">
+        <v>8160</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Cost of Goods Sold (COGS)</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="n">
+        <v>2760.8</v>
+      </c>
+      <c r="D8" s="17" t="n">
+        <v>3352.4</v>
+      </c>
+      <c r="E8" s="17" t="n">
+        <v>3667.9</v>
+      </c>
+      <c r="F8" s="17" t="n">
+        <v>3944</v>
+      </c>
+      <c r="G8" s="18" t="n">
+        <v>4220.1</v>
+      </c>
+      <c r="H8" s="18" t="n">
+        <v>4456.7</v>
+      </c>
+      <c r="I8" s="18" t="n">
+        <v>4653.9</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>Gross Profit</t>
+        </is>
+      </c>
+      <c r="C9" s="15">
+        <f>C7-C8</f>
+        <v/>
+      </c>
+      <c r="D9" s="15">
+        <f>D7-D8</f>
+        <v/>
+      </c>
+      <c r="E9" s="15">
+        <f>E7-E8</f>
+        <v/>
+      </c>
+      <c r="F9" s="15">
+        <f>F7-F8</f>
+        <v/>
+      </c>
+      <c r="G9" s="16">
+        <f>G7-G8</f>
+        <v/>
+      </c>
+      <c r="H9" s="16">
+        <f>H7-H8</f>
+        <v/>
+      </c>
+      <c r="I9" s="16">
+        <f>I7-I8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Gross Margin %</t>
+        </is>
+      </c>
+      <c r="C10" s="19">
+        <f>C9/C7</f>
+        <v/>
+      </c>
+      <c r="D10" s="19">
+        <f>D9/D7</f>
+        <v/>
+      </c>
+      <c r="E10" s="19">
+        <f>E9/E7</f>
+        <v/>
+      </c>
+      <c r="F10" s="19">
+        <f>F9/F7</f>
+        <v/>
+      </c>
+      <c r="G10" s="20">
+        <f>G9/G7</f>
+        <v/>
+      </c>
+      <c r="H10" s="20">
+        <f>H9/H7</f>
+        <v/>
+      </c>
+      <c r="I10" s="20">
+        <f>I9/I7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Selling, General &amp; Administrative (SG&amp;A)</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="n">
+        <v>1444.3</v>
+      </c>
+      <c r="D11" s="17" t="n">
+        <v>1644.9</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>1845.5</v>
+      </c>
+      <c r="F11" s="17" t="n">
+        <v>2006</v>
+      </c>
+      <c r="G11" s="18" t="n">
+        <v>2126.4</v>
+      </c>
+      <c r="H11" s="18" t="n">
+        <v>2246.7</v>
+      </c>
+      <c r="I11" s="18" t="n">
+        <v>2327</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="n">
+        <v>552.5</v>
+      </c>
+      <c r="D12" s="15" t="n">
+        <v>680</v>
+      </c>
+      <c r="E12" s="15" t="n">
+        <v>765</v>
+      </c>
+      <c r="F12" s="15" t="n">
         <v>850</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Benchmark Bond Yield</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>7.95%</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>Total Gross Debt</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>2450</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Price Target / Exit</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>$101.50</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>Net Debt</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="n">
-        <v>1800</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Hard Invalidation Stop</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>$93.00</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>Net Debt / EBITDA</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>2.12x</t>
-        </is>
+      <c r="G12" s="16" t="n">
+        <v>935</v>
+      </c>
+      <c r="H12" s="16" t="n">
+        <v>1003</v>
+      </c>
+      <c r="I12" s="16" t="n">
+        <v>1054</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Earnings &amp; Cash Flow Metric</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>FY Baseline ($M)</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Scenario &amp; Recovery Math</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Implied Bond Value ($)</t>
-        </is>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>EBITDA Margin %</t>
+        </is>
+      </c>
+      <c r="C13" s="21">
+        <f>C12/C7</f>
+        <v/>
+      </c>
+      <c r="D13" s="21">
+        <f>D12/D7</f>
+        <v/>
+      </c>
+      <c r="E13" s="21">
+        <f>E12/E7</f>
+        <v/>
+      </c>
+      <c r="F13" s="21">
+        <f>F12/F7</f>
+        <v/>
+      </c>
+      <c r="G13" s="22">
+        <f>G12/G7</f>
+        <v/>
+      </c>
+      <c r="H13" s="22">
+        <f>H12/H7</f>
+        <v/>
+      </c>
+      <c r="I13" s="22">
+        <f>I12/I7</f>
+        <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="n">
-        <v>7200</v>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>Bull Case (Multiple Expansion / Upgrade)</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>$104.50</t>
-        </is>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Depreciation &amp; Amortization (D&amp;A)</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="n">
+        <v>238</v>
+      </c>
+      <c r="D14" s="17" t="n">
+        <v>261.8</v>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>282.6</v>
+      </c>
+      <c r="F14" s="17" t="n">
+        <v>297.5</v>
+      </c>
+      <c r="G14" s="18" t="n">
+        <v>312.4</v>
+      </c>
+      <c r="H14" s="18" t="n">
+        <v>327.2</v>
+      </c>
+      <c r="I14" s="18" t="n">
+        <v>342.1</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>EBITDA</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="n">
-        <v>850</v>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>Base Case (Pari Passu Debt Servicing)</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>$101.50</t>
-        </is>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>Operating Profit (EBIT)</t>
+        </is>
+      </c>
+      <c r="C15" s="15">
+        <f>C12-C14</f>
+        <v/>
+      </c>
+      <c r="D15" s="15">
+        <f>D12-D14</f>
+        <v/>
+      </c>
+      <c r="E15" s="15">
+        <f>E12-E14</f>
+        <v/>
+      </c>
+      <c r="F15" s="15">
+        <f>F12-F14</f>
+        <v/>
+      </c>
+      <c r="G15" s="16">
+        <f>G12-G14</f>
+        <v/>
+      </c>
+      <c r="H15" s="16">
+        <f>H12-H14</f>
+        <v/>
+      </c>
+      <c r="I15" s="16">
+        <f>I12-I14</f>
+        <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>EBITDA Margin</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>11.8%</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>Stress Case (Sub-Consensus EBITDA)</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>$87.75</t>
-        </is>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Net Interest / Financing Expense</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="n">
+        <v>113.3</v>
+      </c>
+      <c r="D16" s="17" t="n">
+        <v>141.7</v>
+      </c>
+      <c r="E16" s="17" t="n">
+        <v>170</v>
+      </c>
+      <c r="F16" s="17" t="n">
+        <v>188.9</v>
+      </c>
+      <c r="G16" s="18" t="n">
+        <v>181.3</v>
+      </c>
+      <c r="H16" s="18" t="n">
+        <v>173.8</v>
+      </c>
+      <c r="I16" s="18" t="n">
+        <v>166.2</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>Capital Expenditure (Capex)</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="n">
-        <v>450</v>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>Distress / Liquidation Floor (Collateral)</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>$73.12</t>
-        </is>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Profit Before Tax (EBT)</t>
+        </is>
+      </c>
+      <c r="C17" s="17">
+        <f>C15-C16</f>
+        <v/>
+      </c>
+      <c r="D17" s="17">
+        <f>D15-D16</f>
+        <v/>
+      </c>
+      <c r="E17" s="17">
+        <f>E15-E16</f>
+        <v/>
+      </c>
+      <c r="F17" s="17">
+        <f>F15-F16</f>
+        <v/>
+      </c>
+      <c r="G17" s="18">
+        <f>G15-G16</f>
+        <v/>
+      </c>
+      <c r="H17" s="18">
+        <f>H15-H16</f>
+        <v/>
+      </c>
+      <c r="I17" s="18">
+        <f>I15-I16</f>
+        <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>Net Interest Expense</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="n">
-        <v>180</v>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>Net Profit / Income</t>
+        </is>
+      </c>
+      <c r="C18" s="15">
+        <f>C17*0.82</f>
+        <v/>
+      </c>
+      <c r="D18" s="15">
+        <f>D17*0.82</f>
+        <v/>
+      </c>
+      <c r="E18" s="15">
+        <f>E17*0.82</f>
+        <v/>
+      </c>
+      <c r="F18" s="15">
+        <f>F17*0.82</f>
+        <v/>
+      </c>
+      <c r="G18" s="16">
+        <f>G17*0.82</f>
+        <v/>
+      </c>
+      <c r="H18" s="16">
+        <f>H17*0.82</f>
+        <v/>
+      </c>
+      <c r="I18" s="16">
+        <f>I17*0.82</f>
+        <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>II. CASH FLOW &amp; CAPITAL EXPENDITURE (USD M)</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="n"/>
+      <c r="D19" s="13" t="n"/>
+      <c r="E19" s="13" t="n"/>
+      <c r="F19" s="13" t="n"/>
+      <c r="G19" s="13" t="n"/>
+      <c r="H19" s="13" t="n"/>
+      <c r="I19" s="13" t="n"/>
+    </row>
+    <row r="20">
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>Cash Flow from Operations (CFO)</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="n">
+        <v>411.1</v>
+      </c>
+      <c r="D20" s="15" t="n">
+        <v>517.1</v>
+      </c>
+      <c r="E20" s="15" t="n">
+        <v>583.4</v>
+      </c>
+      <c r="F20" s="15" t="n">
+        <v>663</v>
+      </c>
+      <c r="G20" s="16" t="n">
+        <v>729.3</v>
+      </c>
+      <c r="H20" s="16" t="n">
+        <v>782.3</v>
+      </c>
+      <c r="I20" s="16" t="n">
+        <v>828.8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Capital Expenditures (Capex)</t>
+        </is>
+      </c>
+      <c r="C21" s="17" t="n">
+        <v>380.8</v>
+      </c>
+      <c r="D21" s="17" t="n">
+        <v>462.4</v>
+      </c>
+      <c r="E21" s="17" t="n">
+        <v>516.8</v>
+      </c>
+      <c r="F21" s="17" t="n">
+        <v>544</v>
+      </c>
+      <c r="G21" s="18" t="n">
+        <v>571.2</v>
+      </c>
+      <c r="H21" s="18" t="n">
+        <v>554.9</v>
+      </c>
+      <c r="I21" s="18" t="n">
+        <v>533.1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>Free Cash Flow (FCF = CFO - Capex)</t>
+        </is>
+      </c>
+      <c r="C22" s="15">
+        <f>C20-C21</f>
+        <v/>
+      </c>
+      <c r="D22" s="15">
+        <f>D20-D21</f>
+        <v/>
+      </c>
+      <c r="E22" s="15">
+        <f>E20-E21</f>
+        <v/>
+      </c>
+      <c r="F22" s="15">
+        <f>F20-F21</f>
+        <v/>
+      </c>
+      <c r="G22" s="16">
+        <f>G20-G21</f>
+        <v/>
+      </c>
+      <c r="H22" s="16">
+        <f>H20-H21</f>
+        <v/>
+      </c>
+      <c r="I22" s="16">
+        <f>I20-I21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>III. BALANCE SHEET &amp; DEBT METRICS (USD M)</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="n"/>
+      <c r="D23" s="13" t="n"/>
+      <c r="E23" s="13" t="n"/>
+      <c r="F23" s="13" t="n"/>
+      <c r="G23" s="13" t="n"/>
+      <c r="H23" s="13" t="n"/>
+      <c r="I23" s="13" t="n"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Cash &amp; Liquid Equivalents</t>
+        </is>
+      </c>
+      <c r="C24" s="17" t="n">
+        <v>673.2</v>
+      </c>
+      <c r="D24" s="17" t="n">
+        <v>856.8</v>
+      </c>
+      <c r="E24" s="17" t="n">
+        <v>1040.4</v>
+      </c>
+      <c r="F24" s="17" t="n">
+        <v>1224</v>
+      </c>
+      <c r="G24" s="18" t="n">
+        <v>1444.3</v>
+      </c>
+      <c r="H24" s="18" t="n">
+        <v>1652.4</v>
+      </c>
+      <c r="I24" s="18" t="n">
+        <v>1836</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>Gross Debt (Loans + Eurobonds/Sukuk)</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="n">
+        <v>2485.4</v>
+      </c>
+      <c r="D25" s="15" t="n">
+        <v>2690.1</v>
+      </c>
+      <c r="E25" s="15" t="n">
+        <v>2865.5</v>
+      </c>
+      <c r="F25" s="15" t="n">
+        <v>2924</v>
+      </c>
+      <c r="G25" s="16" t="n">
+        <v>2865.5</v>
+      </c>
+      <c r="H25" s="16" t="n">
+        <v>2777.8</v>
+      </c>
+      <c r="I25" s="16" t="n">
+        <v>2631.6</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>Net Debt (Gross Debt - Cash)</t>
+        </is>
+      </c>
+      <c r="C26" s="15">
+        <f>C25-C24</f>
+        <v/>
+      </c>
+      <c r="D26" s="15">
+        <f>D25-D24</f>
+        <v/>
+      </c>
+      <c r="E26" s="15">
+        <f>E25-E24</f>
+        <v/>
+      </c>
+      <c r="F26" s="15">
+        <f>F25-F24</f>
+        <v/>
+      </c>
+      <c r="G26" s="16">
+        <f>G25-G24</f>
+        <v/>
+      </c>
+      <c r="H26" s="16">
+        <f>H25-H24</f>
+        <v/>
+      </c>
+      <c r="I26" s="16">
+        <f>I25-I24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>IV. KEY INSTITUTIONAL CREDIT RATIOS</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="n"/>
+      <c r="D27" s="13" t="n"/>
+      <c r="E27" s="13" t="n"/>
+      <c r="F27" s="13" t="n"/>
+      <c r="G27" s="13" t="n"/>
+      <c r="H27" s="13" t="n"/>
+      <c r="I27" s="13" t="n"/>
+    </row>
+    <row r="28">
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>Net Debt / EBITDA (Net Leverage)</t>
+        </is>
+      </c>
+      <c r="C28" s="23">
+        <f>C26/C12</f>
+        <v/>
+      </c>
+      <c r="D28" s="23">
+        <f>D26/D12</f>
+        <v/>
+      </c>
+      <c r="E28" s="23">
+        <f>E26/E12</f>
+        <v/>
+      </c>
+      <c r="F28" s="23">
+        <f>F26/F12</f>
+        <v/>
+      </c>
+      <c r="G28" s="24">
+        <f>G26/G12</f>
+        <v/>
+      </c>
+      <c r="H28" s="24">
+        <f>H26/H12</f>
+        <v/>
+      </c>
+      <c r="I28" s="24">
+        <f>I26/I12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Gross Debt / EBITDA (Gross Leverage)</t>
+        </is>
+      </c>
+      <c r="C29" s="25">
+        <f>C25/C12</f>
+        <v/>
+      </c>
+      <c r="D29" s="25">
+        <f>D25/D12</f>
+        <v/>
+      </c>
+      <c r="E29" s="25">
+        <f>E25/E12</f>
+        <v/>
+      </c>
+      <c r="F29" s="25">
+        <f>F25/F12</f>
+        <v/>
+      </c>
+      <c r="G29" s="26">
+        <f>G25/G12</f>
+        <v/>
+      </c>
+      <c r="H29" s="26">
+        <f>H25/H12</f>
+        <v/>
+      </c>
+      <c r="I29" s="26">
+        <f>I25/I12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="14" t="inlineStr">
         <is>
           <t>EBITDA / Interest Coverage</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>4.72x</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>Free Cash Flow (FCF)</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="n">
-        <v>220</v>
+      <c r="C30" s="23">
+        <f>C12/C16</f>
+        <v/>
+      </c>
+      <c r="D30" s="23">
+        <f>D12/D16</f>
+        <v/>
+      </c>
+      <c r="E30" s="23">
+        <f>E12/E16</f>
+        <v/>
+      </c>
+      <c r="F30" s="23">
+        <f>F12/F16</f>
+        <v/>
+      </c>
+      <c r="G30" s="24">
+        <f>G12/G16</f>
+        <v/>
+      </c>
+      <c r="H30" s="24">
+        <f>H12/H16</f>
+        <v/>
+      </c>
+      <c r="I30" s="24">
+        <f>I12/I16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>CFO / Net Debt %</t>
+        </is>
+      </c>
+      <c r="C31" s="19">
+        <f>C20/C26</f>
+        <v/>
+      </c>
+      <c r="D31" s="19">
+        <f>D20/D26</f>
+        <v/>
+      </c>
+      <c r="E31" s="19">
+        <f>E20/E26</f>
+        <v/>
+      </c>
+      <c r="F31" s="19">
+        <f>F20/F26</f>
+        <v/>
+      </c>
+      <c r="G31" s="20">
+        <f>G20/G26</f>
+        <v/>
+      </c>
+      <c r="H31" s="20">
+        <f>H20/H26</f>
+        <v/>
+      </c>
+      <c r="I31" s="20">
+        <f>I20/I26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Capex / Revenue %</t>
+        </is>
+      </c>
+      <c r="C32" s="19">
+        <f>C21/C7</f>
+        <v/>
+      </c>
+      <c r="D32" s="19">
+        <f>D21/D7</f>
+        <v/>
+      </c>
+      <c r="E32" s="19">
+        <f>E21/E7</f>
+        <v/>
+      </c>
+      <c r="F32" s="19">
+        <f>F21/F7</f>
+        <v/>
+      </c>
+      <c r="G32" s="20">
+        <f>G21/G7</f>
+        <v/>
+      </c>
+      <c r="H32" s="20">
+        <f>H21/H7</f>
+        <v/>
+      </c>
+      <c r="I32" s="20">
+        <f>I21/I7</f>
+        <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>